--- a/public/exportTemplates/groups.xlsx
+++ b/public/exportTemplates/groups.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TempShare\KYVL_CC_Plus\Export samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A9519C-BA22-4673-857C-E557F28E1B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47599ACF-C513-4F39-BC87-BB6C6762AEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6525" yWindow="4245" windowWidth="30675" windowHeight="14385" xr2:uid="{B9EF07C2-5FC7-4CE7-9673-D90604365E4E}"/>
+    <workbookView xWindow="11160" yWindow="2835" windowWidth="15750" windowHeight="15795" xr2:uid="{B9EF07C2-5FC7-4CE7-9673-D90604365E4E}"/>
   </bookViews>
   <sheets>
     <sheet name="HowToImport" sheetId="1" r:id="rId1"/>
@@ -30,12 +30,6 @@
     <t xml:space="preserve"> * The Institution Groups tab represents a starting place for updating or importing settings.</t>
   </si>
   <si>
-    <t xml:space="preserve"> * Any Import rows without an ID in column A will be ignored.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> * If required values are missing/invalid within a given row, the row will be ignored.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> * Once the data sheet is ready to import, save the sheet as a CSV and import it into CC-Plus.</t>
   </si>
   <si>
@@ -79,6 +73,12 @@
   </si>
   <si>
     <t>Institution Group Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * Rows with an ID in column A that matches an existing ID will have the name updated to the value in column B.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * Any Import rows without an ID in column A and a Name in column B will be ignored.</t>
   </si>
 </sst>
 </file>
@@ -208,15 +208,6 @@
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -226,6 +217,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -536,19 +536,19 @@
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="3"/>
+      <c r="A1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -564,7 +564,7 @@
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -576,7 +576,7 @@
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -588,7 +588,7 @@
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -600,7 +600,7 @@
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -612,7 +612,7 @@
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -634,48 +634,48 @@
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="D10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="E10" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="C11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
         <v>15</v>
       </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>14</v>
+      <c r="D12" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -686,9 +686,9 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:H4"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A4:H4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
